--- a/branches/master/StructureDefinition-hiv-patient.xlsx
+++ b/branches/master/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-27T13:30:57+00:00</t>
+    <t>2023-04-28T11:34:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-patient.xlsx
+++ b/branches/master/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:34:44+00:00</t>
+    <t>2023-04-30T04:59:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-patient.xlsx
+++ b/branches/master/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T04:59:44+00:00</t>
+    <t>2023-05-01T18:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-patient.xlsx
+++ b/branches/master/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T18:23:44+00:00</t>
+    <t>2023-05-03T04:38:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-patient.xlsx
+++ b/branches/master/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T04:38:57+00:00</t>
+    <t>2023-05-04T06:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-patient.xlsx
+++ b/branches/master/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T06:27:52+00:00</t>
+    <t>2023-05-05T18:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-patient.xlsx
+++ b/branches/master/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:22:20+00:00</t>
+    <t>2023-05-05T18:27:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-patient.xlsx
+++ b/branches/master/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:52:16+00:00</t>
+    <t>2023-05-06T12:19:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3485,7 +3485,7 @@
         <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>182</v>
@@ -3986,13 +3986,13 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>80</v>
@@ -4109,7 +4109,7 @@
         <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>80</v>
@@ -4805,13 +4805,13 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>80</v>

--- a/branches/master/StructureDefinition-hiv-patient.xlsx
+++ b/branches/master/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:19:14+00:00</t>
+    <t>2023-05-07T12:14:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-patient.xlsx
+++ b/branches/master/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:14:35+00:00</t>
+    <t>2023-05-07T13:36:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-patient.xlsx
+++ b/branches/master/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:36:00+00:00</t>
+    <t>2023-05-08T07:05:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-patient.xlsx
+++ b/branches/master/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T07:05:14+00:00</t>
+    <t>2023-05-08T20:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-patient.xlsx
+++ b/branches/master/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T20:00:55+00:00</t>
+    <t>2023-05-08T21:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-patient.xlsx
+++ b/branches/master/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:02:34+00:00</t>
+    <t>2023-05-11T19:57:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-patient.xlsx
+++ b/branches/master/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:57:24+00:00</t>
+    <t>2023-05-11T20:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-patient.xlsx
+++ b/branches/master/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:42:55+00:00</t>
+    <t>2023-05-12T08:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-patient.xlsx
+++ b/branches/master/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T08:27:31+00:00</t>
+    <t>2023-05-12T10:53:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-patient.xlsx
+++ b/branches/master/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:53:52+00:00</t>
+    <t>2023-05-12T13:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-patient.xlsx
+++ b/branches/master/StructureDefinition-hiv-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:58:20+00:00</t>
+    <t>2023-05-23T09:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
